--- a/data/file_generation/reference/data_81/七年级标准_分数换算_精确 2 位小数版_res.xlsx
+++ b/data/file_generation/reference/data_81/七年级标准_分数换算_精确 2 位小数版_res.xlsx
@@ -1016,26 +1016,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08D32780-46AB-4DE0-BEF4-BD2ECE0A1E3B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C0B9856-9A1D-4B98-A4D9-35AEC20D24AF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{191E5E32-C775-44DD-87D6-EE919CF93ABE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A40E2F76-4E12-4812-82B0-6FF90044937C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{093C5D61-1F35-4492-904C-EA0D0A4EAFFC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F0F5C0B-14C2-4883-9D93-CCD2DC8B87D9}"/>
 </file>